--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484306_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484306_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3375</v>
+        <v>4.6201</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1149</v>
+        <v>3.6698</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2226</v>
+        <v>0.9502</v>
       </c>
       <c r="G2" t="n">
         <v>1.2335</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5765</v>
+        <v>0.8591</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7567</v>
+        <v>0.3117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8198</v>
+        <v>0.5474</v>
       </c>
       <c r="V2" t="n">
         <v>1.5507</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.568</v>
+        <v>4.5352</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0314</v>
+        <v>0.8897</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5365</v>
+        <v>3.6455</v>
       </c>
       <c r="G3" t="n">
         <v>2.0731</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4633</v>
+        <v>0.4305</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8448</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3815</v>
+        <v>-0.2726</v>
       </c>
       <c r="V3" t="n">
         <v>0.6642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5331</v>
+        <v>2.0101</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8693</v>
+        <v>-1.011</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4024</v>
+        <v>3.0211</v>
       </c>
       <c r="G4" t="n">
         <v>4.3821</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>1.468</v>
+        <v>0.945</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1337</v>
+        <v>0.992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3343</v>
+        <v>-0.047</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3869</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4472</v>
+        <v>1.1148</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0326</v>
+        <v>-1.1743</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4798</v>
+        <v>2.2891</v>
       </c>
       <c r="G5" t="n">
         <v>2.3816</v>
@@ -844,13 +844,13 @@
         <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9018</v>
+        <v>0.5694</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0126</v>
+        <v>0.8709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1108</v>
+        <v>-0.3015</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6642</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6345</v>
+        <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9154</v>
+        <v>1.4703</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2809</v>
+        <v>-1.0903</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8003</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9306</v>
+        <v>0.6762</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8778</v>
+        <v>0.4327</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0528</v>
+        <v>0.2434</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0262</v>
+        <v>-0.2236</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0362</v>
+        <v>0.1091</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0101</v>
+        <v>-0.3327</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.886</v>
+        <v>-0.4293</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6655</v>
+        <v>-0.3083</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7795</v>
+        <v>-0.121</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5307</v>
+        <v>1.0039</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6926</v>
+        <v>0.4502</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>0.5537</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6448</v>
+        <v>-1.4332</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9729</v>
+        <v>-0.7585</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6176</v>
+        <v>-0.6747</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>0.805</v>
+        <v>0.401</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.0819</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1471</v>
+        <v>0.3191</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8442</v>
+        <v>-0.3113</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.457</v>
+        <v>-1.8807</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3872</v>
+        <v>1.5695</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4293</v>
+        <v>1.6723</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3083</v>
+        <v>1.24</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.121</v>
+        <v>0.4323</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0039</v>
+        <v>0.8182</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4502</v>
+        <v>1.5989</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5537</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4332</v>
+        <v>0.8541</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7585</v>
+        <v>-0.3589</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6747</v>
+        <v>1.213</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2196</v>
+        <v>0.0165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4842</v>
+        <v>0.4266</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2646</v>
+        <v>-0.4101</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6709</v>
+        <v>-0.413</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7502</v>
+        <v>-2.1779</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0792</v>
+        <v>1.7649</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6723</v>
+        <v>-1.886</v>
       </c>
       <c r="H9" t="n">
-        <v>1.24</v>
+        <v>-3.6655</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4323</v>
+        <v>1.7795</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8182</v>
+        <v>-2.5307</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5989</v>
+        <v>-2.6926</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.1619</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8541</v>
+        <v>0.6448</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3589</v>
+        <v>-0.9729</v>
       </c>
       <c r="O9" t="n">
-        <v>1.213</v>
+        <v>1.6176</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3432</v>
+        <v>0.4181</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4429</v>
+        <v>0.8104</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9003</v>
+        <v>-0.3923</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8622</v>
+        <v>-1.2144</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5907</v>
+        <v>-0.0246</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2715</v>
+        <v>-1.1898</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4981</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6526</v>
+        <v>-0.0048</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5309</v>
+        <v>0.0352</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1217</v>
+        <v>-0.04</v>
       </c>
       <c r="V10" t="n">
         <v>3.0466</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.482</v>
+        <v>-5.2581</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1347</v>
+        <v>-4.0741</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3473</v>
+        <v>-1.1839</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1301</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2108</v>
+        <v>0.4347</v>
       </c>
       <c r="T11" t="n">
-        <v>0.311</v>
+        <v>0.3715</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1002</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.634799999999999</v>
+        <v>5.239800000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.808999999999999</v>
+        <v>-4.2037</v>
       </c>
       <c r="F12" t="n">
-        <v>9.443700000000002</v>
+        <v>9.4436</v>
       </c>
       <c r="G12" t="n">
         <v>1.998799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.0689</v>
+        <v>-4.068900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>6.0679</v>
+        <v>6.067900000000002</v>
       </c>
       <c r="J12" t="n">
         <v>6.616300000000001</v>
@@ -1390,13 +1390,13 @@
         <v>15.6276</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1406</v>
+        <v>4.7457</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4307</v>
+        <v>5.036</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2901</v>
+        <v>-0.2904</v>
       </c>
       <c r="V12" t="n">
         <v>3.3788</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2254</v>
+        <v>7.1502</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3724</v>
+        <v>5.2713</v>
       </c>
       <c r="F13" t="n">
-        <v>1.853</v>
+        <v>1.8789</v>
       </c>
       <c r="G13" t="n">
         <v>6.6791</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.351</v>
+        <v>0.2758</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1294</v>
+        <v>0.0283</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2216</v>
+        <v>0.2475</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7092</v>
+        <v>4.8773</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4449</v>
+        <v>3.1527</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2643</v>
+        <v>1.7246</v>
       </c>
       <c r="G14" t="n">
         <v>1.0352</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.631</v>
+        <v>-0.4629</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.773</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.858</v>
+        <v>-0.3977</v>
       </c>
       <c r="V14" t="n">
         <v>2.547</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7627</v>
+        <v>0.7692</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7075</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0553</v>
+        <v>0.1628</v>
       </c>
       <c r="G15" t="n">
         <v>0.9955000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4364</v>
+        <v>-0.4299</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1732</v>
+        <v>-0.2743</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2632</v>
+        <v>-0.1556</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1638</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.2525</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2512</v>
+        <v>-1.5219</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7991</v>
+        <v>1.2694</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7131999999999999</v>
+        <v>1.9368</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8511</v>
+        <v>0.2912</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5643</v>
+        <v>1.6457</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3371</v>
+        <v>1.4872</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0422</v>
+        <v>0.2456</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2949</v>
+        <v>1.2416</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6239</v>
+        <v>0.4496</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8933</v>
+        <v>0.0456</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>0.4041</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7104</v>
+        <v>-0.822</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3631</v>
+        <v>-0.079</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3473</v>
+        <v>-0.743</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7479</v>
+        <v>-0.329</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4208</v>
+        <v>-1.7823</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6729000000000001</v>
+        <v>1.4533</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9368</v>
+        <v>-1.5335</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2912</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6457</v>
+        <v>-0.8364</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4872</v>
+        <v>-0.23</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2456</v>
+        <v>-0.2034</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2416</v>
+        <v>-0.0266</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4496</v>
+        <v>-1.3034</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0456</v>
+        <v>-0.4937</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>-0.8097</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3173</v>
+        <v>-0.2448</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0221</v>
+        <v>0.124</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3394</v>
+        <v>-0.3688</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9486</v>
+        <v>-0.6024</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1867</v>
+        <v>1.2512</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2381</v>
+        <v>-1.8536</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5335</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.8511</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8364</v>
+        <v>1.5643</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.23</v>
+        <v>1.3371</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2034</v>
+        <v>0.0422</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0266</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3034</v>
+        <v>-0.6239</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4937</v>
+        <v>-0.8933</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8097</v>
+        <v>0.2694</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.7649</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2805</v>
+        <v>-0.3631</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5839</v>
+        <v>-0.4017</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
         <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1842</v>
+        <v>-1.9755</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6822</v>
+        <v>-4.5811</v>
       </c>
       <c r="F19" t="n">
-        <v>2.498</v>
+        <v>2.6056</v>
       </c>
       <c r="G19" t="n">
         <v>-2.176</v>
@@ -1936,13 +1936,13 @@
         <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0699</v>
+        <v>0.2786</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1732</v>
+        <v>-0.0721</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2431</v>
+        <v>0.3507</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6642</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8021</v>
+        <v>-2.9374</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5658</v>
+        <v>-2.1614</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2363</v>
+        <v>-0.776</v>
       </c>
       <c r="G20" t="n">
         <v>0.3207</v>
@@ -2014,13 +2014,13 @@
         <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5759</v>
+        <v>-0.7111</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2805</v>
+        <v>0.124</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2954</v>
+        <v>-0.8351</v>
       </c>
       <c r="V20" t="n">
         <v>-2.547</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8984</v>
+        <v>-3.306</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3482</v>
+        <v>-3.9437</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4498</v>
+        <v>0.6377</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1667</v>
@@ -2092,13 +2092,13 @@
         <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0061</v>
+        <v>0.5984</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2337</v>
+        <v>0.1707</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2398</v>
+        <v>0.4277</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2029</v>
+        <v>-6.0063</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0159</v>
+        <v>-5.7348</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1871</v>
+        <v>-0.2715</v>
       </c>
       <c r="G22" t="n">
         <v>-5.8034</v>
@@ -2170,13 +2170,13 @@
         <v>2.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9678</v>
+        <v>0.1645</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4159</v>
+        <v>0.697</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4481</v>
+        <v>-0.5325</v>
       </c>
       <c r="V22" t="n">
         <v>0.6093</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6347</v>
+        <v>-2.6124</v>
       </c>
       <c r="E23" t="n">
         <v>-9.4436</v>
       </c>
       <c r="F23" t="n">
-        <v>4.8089</v>
+        <v>6.8312</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.999099999999999</v>
+        <v>-1.9991</v>
       </c>
       <c r="H23" t="n">
-        <v>4.069099999999998</v>
+        <v>4.0691</v>
       </c>
       <c r="I23" t="n">
         <v>-6.0678</v>
@@ -2227,7 +2227,7 @@
         <v>7.982800000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.365400000000001</v>
+        <v>-3.3654</v>
       </c>
       <c r="M23" t="n">
         <v>-6.616199999999999</v>
@@ -2248,13 +2248,13 @@
         <v>20.511</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.140599999999999</v>
+        <v>-2.1183</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2902000000000005</v>
+        <v>0.2903</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.430800000000001</v>
+        <v>-2.4085</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3788</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484306_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484306_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +653,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5352</v>
+        <v>3.9282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8897</v>
+        <v>0.2828</v>
       </c>
       <c r="F3" t="n">
         <v>3.6455</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0731</v>
+        <v>1.4661</v>
       </c>
       <c r="H3" t="n">
         <v>-1.1233</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1964</v>
+        <v>2.5894</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3587</v>
+        <v>0.7517</v>
       </c>
       <c r="K3" t="n">
         <v>-0.4899</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8486</v>
+        <v>1.2416</v>
       </c>
       <c r="M3" t="n">
         <v>0.7144</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.38</v>
+        <v>0.914</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4703</v>
+        <v>0.914</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0903</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8003</v>
+        <v>0.914</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3684</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4319</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0376</v>
+        <v>0.914</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3901</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6475</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8379</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7585</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0793</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6762</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4327</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2434</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2236</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1091</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3327</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4293</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3083</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.121</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0039</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4502</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5537</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4332</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7585</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.401</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3191</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3113</v>
+        <v>0.607</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8807</v>
+        <v>0.607</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5695</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6723</v>
+        <v>0.607</v>
       </c>
       <c r="H8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4323</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8182</v>
+        <v>0.607</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5989</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8541</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3589</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.213</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0165</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4266</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4101</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.413</v>
+        <v>-0.2269</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1779</v>
+        <v>0.8633</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7649</v>
+        <v>-1.0903</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.886</v>
+        <v>-1.4073</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.6655</v>
+        <v>-0.3684</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7795</v>
+        <v>-1.0389</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5307</v>
+        <v>0.4306</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6926</v>
+        <v>0.3901</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6448</v>
+        <v>-1.8379</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9729</v>
+        <v>-0.7585</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6176</v>
+        <v>-1.0793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4181</v>
+        <v>0.6762</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8104</v>
+        <v>0.4327</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3923</v>
+        <v>0.2434</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2144</v>
+        <v>-0.3113</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0246</v>
+        <v>-1.8807</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1898</v>
+        <v>1.5695</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4981</v>
+        <v>1.6723</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7923</v>
+        <v>1.24</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2904</v>
+        <v>0.4323</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1762</v>
+        <v>0.8182</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4392</v>
+        <v>1.5989</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6155</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3219</v>
+        <v>0.8541</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.647</v>
+        <v>-0.3589</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6749000000000001</v>
+        <v>1.213</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0048</v>
+        <v>0.0165</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0352</v>
+        <v>0.4266</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.04</v>
+        <v>-0.4101</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0466</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2581</v>
+        <v>-0.413</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0741</v>
+        <v>-2.1779</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1839</v>
+        <v>1.7649</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1301</v>
+        <v>-1.886</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4958</v>
+        <v>-3.6655</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6342</v>
+        <v>1.7795</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4922</v>
+        <v>-2.5307</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.5327</v>
+        <v>-2.6926</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>0.1619</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6379</v>
+        <v>0.6448</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9729</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6747</v>
+        <v>1.6176</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4347</v>
+        <v>0.4181</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3715</v>
+        <v>0.8104</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.3923</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,370 +1400,386 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.239800000000002</v>
+        <v>-1.1376</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2037</v>
+        <v>-0.8048</v>
       </c>
       <c r="F12" t="n">
-        <v>9.4436</v>
+        <v>-0.3327</v>
       </c>
       <c r="G12" t="n">
-        <v>1.998799999999999</v>
+        <v>-1.3432</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.068900000000001</v>
+        <v>-0.6152</v>
       </c>
       <c r="I12" t="n">
-        <v>6.067900000000002</v>
+        <v>-0.728</v>
       </c>
       <c r="J12" t="n">
-        <v>6.616300000000001</v>
+        <v>0.09</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9138</v>
+        <v>0.1433</v>
       </c>
       <c r="L12" t="n">
-        <v>2.7024</v>
+        <v>-0.0533</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.6173</v>
+        <v>-1.4332</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.982799999999999</v>
+        <v>-0.7585</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3656</v>
+        <v>-0.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.8835</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-20.5109</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>15.6276</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7457</v>
+        <v>0.401</v>
       </c>
       <c r="T12" t="n">
-        <v>5.036</v>
+        <v>0.0819</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2904</v>
+        <v>0.3191</v>
       </c>
       <c r="V12" t="n">
-        <v>3.3788</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.655200000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2763</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1502</v>
+        <v>-1.2144</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2713</v>
+        <v>-0.0246</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8789</v>
+        <v>-1.1898</v>
       </c>
       <c r="G13" t="n">
-        <v>6.6791</v>
+        <v>-2.4981</v>
       </c>
       <c r="H13" t="n">
-        <v>6.248</v>
+        <v>0.7923</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4311</v>
+        <v>-3.2904</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2197</v>
+        <v>-0.1762</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0579</v>
+        <v>2.4392</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1619</v>
+        <v>-2.6155</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4593</v>
+        <v>-2.3219</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1901</v>
+        <v>-1.647</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2692</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2758</v>
+        <v>-0.0048</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0283</v>
+        <v>0.0352</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2475</v>
+        <v>-0.04</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8773</v>
+        <v>-5.2581</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1527</v>
+        <v>-4.0741</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7246</v>
+        <v>-1.1839</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0352</v>
+        <v>-4.1301</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9136</v>
+        <v>-3.4958</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1216</v>
+        <v>-0.6342</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9993</v>
+        <v>-2.4922</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7982</v>
+        <v>-2.5327</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2011</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9641</v>
+        <v>-1.6379</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1154</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0795</v>
+        <v>-0.6747</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4629</v>
+        <v>0.4347</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.3715</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3977</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.547</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7692</v>
+        <v>5.2399</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6064000000000001</v>
+        <v>-4.2035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1628</v>
+        <v>9.4436</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.998900000000003</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5083</v>
+        <v>-4.0688</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5128</v>
+        <v>6.0679</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8807</v>
+        <v>6.616400000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3929</v>
+        <v>3.9139</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5122</v>
+        <v>2.702400000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1148</v>
+        <v>-4.6173</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1154</v>
+        <v>-7.982799999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>3.365600000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-4.8835</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-20.5109</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>15.6276</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4299</v>
+        <v>4.7457</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2743</v>
+        <v>5.036</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1556</v>
+        <v>-0.2904</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1638</v>
+        <v>3.3788</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.655200000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1638</v>
-      </c>
+        <v>-1.2763</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2525</v>
+        <v>7.1502</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5219</v>
+        <v>5.2713</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2694</v>
+        <v>1.8789</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9368</v>
+        <v>6.6791</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2912</v>
+        <v>6.248</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6457</v>
+        <v>0.4311</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4872</v>
+        <v>6.2197</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2456</v>
+        <v>6.0579</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2416</v>
+        <v>0.1619</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4496</v>
+        <v>0.4593</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0456</v>
+        <v>0.1901</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4041</v>
+        <v>0.2692</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.822</v>
+        <v>0.2758</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.079</v>
+        <v>0.0283</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.743</v>
+        <v>0.2475</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1718,240 +1789,260 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.329</v>
+        <v>4.8773</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7823</v>
+        <v>3.1527</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4533</v>
+        <v>1.7246</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5335</v>
+        <v>1.0352</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6971000000000001</v>
+        <v>0.9136</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8364</v>
+        <v>0.1216</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.23</v>
+        <v>1.9993</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2034</v>
+        <v>0.7982</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0266</v>
+        <v>1.2011</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3034</v>
+        <v>-0.9641</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4937</v>
+        <v>0.1154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8097</v>
+        <v>-1.0795</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1255</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2448</v>
+        <v>-0.4629</v>
       </c>
       <c r="T17" t="n">
-        <v>0.124</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3688</v>
+        <v>-0.3977</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>2.547</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6024</v>
+        <v>0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2512</v>
+        <v>0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8536</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8511</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5643</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3371</v>
+        <v>0.914</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0422</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2949</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6239</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8933</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7649</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3631</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4017</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9755</v>
+        <v>0.7692</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5811</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6056</v>
+        <v>0.1628</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.176</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7741</v>
+        <v>1.5083</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4019</v>
+        <v>-0.5128</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8914</v>
+        <v>0.8807</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4899</v>
+        <v>1.3929</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4015</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2846</v>
+        <v>0.1148</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2842</v>
+        <v>0.1154</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2786</v>
+        <v>-0.4299</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0721</v>
+        <v>-0.2743</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3507</v>
+        <v>-0.1556</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6642</v>
+        <v>-1.1638</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1962,309 +2053,740 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9374</v>
+        <v>0.614</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1614</v>
+        <v>0.614</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.776</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3207</v>
+        <v>0.614</v>
       </c>
       <c r="H20" t="n">
-        <v>2.438</v>
+        <v>0.614</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1172</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9731</v>
+        <v>0.614</v>
       </c>
       <c r="K20" t="n">
-        <v>3.955</v>
+        <v>0.614</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9818</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6524</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.517</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7111</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8351</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.547</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.306</v>
+        <v>-0.2525</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9437</v>
+        <v>-1.5219</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6377</v>
+        <v>1.2694</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1667</v>
+        <v>1.9368</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.2912</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5189</v>
+        <v>1.6457</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1377</v>
+        <v>1.4872</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4285</v>
+        <v>0.2456</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7092</v>
+        <v>1.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0289</v>
+        <v>0.4496</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2192</v>
+        <v>0.0456</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8097</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5984</v>
+        <v>-0.822</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1707</v>
+        <v>-0.079</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4277</v>
+        <v>-0.743</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0063</v>
+        <v>-0.6024</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7348</v>
+        <v>1.2512</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2715</v>
+        <v>-1.8536</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.8034</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.36</v>
+        <v>-0.8511</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4433</v>
+        <v>1.5643</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.0208</v>
+        <v>1.3371</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.3872</v>
+        <v>0.0422</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.2949</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7826</v>
+        <v>-0.6239</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9729</v>
+        <v>-0.8933</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8097</v>
+        <v>0.2694</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9301</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1645</v>
+        <v>-0.7649</v>
       </c>
       <c r="T22" t="n">
-        <v>0.697</v>
+        <v>-0.3631</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5325</v>
+        <v>-0.4017</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6093</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6124</v>
+        <v>-1.2429</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.4436</v>
+        <v>-2.6962</v>
       </c>
       <c r="F23" t="n">
+        <v>1.4533</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.4474</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.0041</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.4433</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.144</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.5104</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.3034</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.4937</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.1255</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.2448</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3688</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I. ISERN CASES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.9755</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.5811</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.6056</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.176</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.7741</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.4019</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.8914</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.4899</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.4015</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.2846</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2842</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0721</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. JAIME BATLLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.306</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.9437</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.1667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.6477000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-3.5189</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.1377</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.4285</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.7092</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.0289</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2192</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.5514</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.7753</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.776</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.2933</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.1172</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.3592</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.341</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.6524</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.7111</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.8351</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.547</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F. VILAR FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-6.0063</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.7348</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.2715</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5.8034</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.4433</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-4.0208</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-3.3872</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.7826</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.9729</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.5325</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484306_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.612300000000002</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-9.4434</v>
+      </c>
+      <c r="F28" t="n">
         <v>6.8312</v>
       </c>
-      <c r="G23" t="n">
-        <v>-1.9991</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.0691</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-6.0678</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.6172</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="G28" t="n">
+        <v>-1.998999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.069100000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-6.067699999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.617299999999998</v>
+      </c>
+      <c r="K28" t="n">
         <v>7.982800000000001</v>
       </c>
-      <c r="L23" t="n">
-        <v>-3.3654</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L28" t="n">
+        <v>-3.365400000000001</v>
+      </c>
+      <c r="M28" t="n">
         <v>-6.616199999999999</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N28" t="n">
         <v>-3.9138</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O28" t="n">
         <v>-2.7023</v>
       </c>
-      <c r="P23" t="n">
-        <v>4.883599999999999</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P28" t="n">
+        <v>4.8836</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R28" t="n">
         <v>20.511</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S28" t="n">
         <v>-2.1183</v>
       </c>
-      <c r="T23" t="n">
-        <v>0.2903</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="T28" t="n">
+        <v>0.2902999999999999</v>
+      </c>
+      <c r="U28" t="n">
         <v>-2.4085</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V28" t="n">
         <v>-3.3788</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W28" t="n">
         <v>1.2764</v>
       </c>
-      <c r="X23" t="n">
-        <v>-4.655099999999999</v>
-      </c>
+      <c r="X28" t="n">
+        <v>-4.6551</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
